--- a/site/American-Express-Okta-Integration-Guide/headings.xlsx
+++ b/site/American-Express-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,41 +649,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,32 +759,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/American-Express-Okta-Integration-Guide/headings.xlsx
+++ b/site/American-Express-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,108 +661,306 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Card Application Request Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KNRSTJN3A8JQKGV8PX4YA42X</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRSTJN3A8JQKGV8PX4YA42X</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KNRSTJN3Q7DZWMJ0GEKWKWCF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRSTJN3Q7DZWMJ0GEKWKWCF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Integration Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KNRSTJN3AVXZ9V1TCH6RZDPP</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRSTJN3AVXZ9V1TCH6RZDPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KNRSHJ66RW8KG8MQVWT2BZT5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRSHJ66RW8KG8MQVWT2BZT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KNRSTJN3X10V5Q7RX07KG1XG</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRSTJN3X10V5Q7RX07KG1XG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KNRSTJN3V91CYJFDB7FQ8XHH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01KNRSTJN3V91CYJFDB7FQ8XHH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/American-Express-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
